--- a/2_Formulas_Functions/9_Date_Time_Functions.xlsx
+++ b/2_Formulas_Functions/9_Date_Time_Functions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmous\Downloads\Excel_Data_Analytics_Course-main\Excel_Data_Analytics_Course-main\2_Formulas_Functions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f943803864469b1e/Documents/GitHub/Excel_Data_Analytics/Excel_project_data_analysis/2_Formulas_Functions/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA4F63A-A13B-484B-87B6-0DBCB27285B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="795" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="8" r:id="rId1"/>
@@ -2661,11 +2661,11 @@
       </c>
       <c r="P2" s="9">
         <f ca="1">TODAY()</f>
-        <v>46247</v>
+        <v>46286</v>
       </c>
       <c r="R2">
         <f ca="1">DATEDIF(D2,$P$2,"D")</f>
-        <v>1276</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="R3">
         <f ca="1">DATEDIF(D3,$P$2,"D")</f>
-        <v>1192</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="R4">
         <f t="shared" ref="R4:R21" ca="1" si="4">DATEDIF(D4,$P$2,"D")</f>
-        <v>1119</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="R5">
         <f t="shared" ca="1" si="4"/>
-        <v>1074</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="R6">
         <f t="shared" ca="1" si="4"/>
-        <v>999</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="R7">
         <f t="shared" ca="1" si="4"/>
-        <v>945</v>
+        <v>984</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
@@ -2942,7 +2942,7 @@
       <c r="P8" s="9"/>
       <c r="R8">
         <f t="shared" ca="1" si="4"/>
-        <v>893</v>
+        <v>932</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="R9">
         <f t="shared" ca="1" si="4"/>
-        <v>839</v>
+        <v>878</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="R10">
         <f t="shared" ca="1" si="4"/>
-        <v>789</v>
+        <v>828</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="R11">
         <f t="shared" ca="1" si="4"/>
-        <v>767</v>
+        <v>806</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="R12">
         <f t="shared" ca="1" si="4"/>
-        <v>792</v>
+        <v>831</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="R13">
         <f t="shared" ca="1" si="4"/>
-        <v>1296</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="R14">
         <f t="shared" ca="1" si="4"/>
-        <v>1245</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="R15">
         <f t="shared" ca="1" si="4"/>
-        <v>1169</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="R16">
         <f t="shared" ca="1" si="4"/>
-        <v>1079</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="R17">
         <f t="shared" ca="1" si="4"/>
-        <v>1029</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="R18">
         <f t="shared" ca="1" si="4"/>
-        <v>897</v>
+        <v>936</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="R19">
         <f t="shared" ca="1" si="4"/>
-        <v>829</v>
+        <v>868</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="R20">
         <f t="shared" ca="1" si="4"/>
-        <v>751</v>
+        <v>790</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="R21">
         <f t="shared" ca="1" si="4"/>
-        <v>825</v>
+        <v>864</v>
       </c>
     </row>
   </sheetData>
